--- a/Assets/Samples/IAPDemo/Excels/Networks/HostKeys/NetworkHostKeys.xlsx
+++ b/Assets/Samples/IAPDemo/Excels/Networks/HostKeys/NetworkHostKeys.xlsx
@@ -1,143 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SoloGames-X\nova\Assets\Samples\IAPDemo\Excels\Networks\HostKeys\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989FC00E-6A98-41B8-B654-8082687EFBD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8126" yWindow="3060" windowWidth="24077" windowHeight="13157" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8126" yWindow="3060" windowWidth="24077" windowHeight="13157" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NetworkHostKeys" sheetId="1" r:id="rId1"/>
+    <sheet name="NetworkHostKeys-Debug" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NetworkHostKeys-Release" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>网络域名表（NetHosts）</t>
-  </si>
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>#Desc</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>主机唯一标识名</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>GameServer</t>
-  </si>
-  <si>
-    <t>游戏服务器域名</t>
-  </si>
-  <si>
-    <t>https://t-solo-api-game.ahameet.com</t>
-  </si>
-  <si>
-    <t>TGAServer</t>
-  </si>
-  <si>
-    <t>IAPServer</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏支付服务器域名</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://report.lolipopmobi.com</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://t-pay-v3.ahameet.com</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <color rgb="FF000000"/>
       <sz val="9.75"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9.75"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <name val="宋体"/>
+      <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="9.75"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -212,34 +137,34 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -247,16 +172,75 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -544,204 +528,505 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X43"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="13" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="24" width="37" style="3" customWidth="1"/>
-    <col min="25" max="16384" width="13" style="2"/>
+    <col width="12" customWidth="1" style="1" min="1" max="1"/>
+    <col width="37" customWidth="1" style="3" min="2" max="24"/>
+    <col width="13" customWidth="1" style="2" min="25" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-    </row>
-    <row r="2" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-    </row>
-    <row r="3" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-    </row>
-    <row r="4" spans="1:24" s="1" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>网络域名表（NetHosts）</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="4" t="n"/>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="4" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="4" t="n"/>
+      <c r="W1" s="4" t="n"/>
+      <c r="X1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>#Desc</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+      <c r="P2" s="5" t="n"/>
+      <c r="Q2" s="5" t="n"/>
+      <c r="R2" s="5" t="n"/>
+      <c r="S2" s="5" t="n"/>
+      <c r="T2" s="5" t="n"/>
+      <c r="U2" s="5" t="n"/>
+      <c r="V2" s="5" t="n"/>
+      <c r="W2" s="5" t="n"/>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
+      <c r="N3" s="6" t="n"/>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="6" t="n"/>
+      <c r="Q3" s="6" t="n"/>
+      <c r="R3" s="6" t="n"/>
+      <c r="S3" s="6" t="n"/>
+      <c r="T3" s="6" t="n"/>
+      <c r="U3" s="6" t="n"/>
+      <c r="V3" s="6" t="n"/>
+      <c r="W3" s="6" t="n"/>
+      <c r="X3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="22" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>主机唯一标识名</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>GameServer</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>游戏服务器域名</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>https://t-solo-api-game.ahameet.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>TGAServer</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>游戏服务器域名</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>https://report.lolipopmobi.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>IAPServer</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>游戏支付服务器域名</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>https://t-pay-v3.ahameet.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1"/>
+    <row r="9" ht="22" customHeight="1"/>
+    <row r="10" ht="22" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1"/>
+    <row r="12" ht="22" customHeight="1"/>
+    <row r="13" ht="22" customHeight="1"/>
+    <row r="14" ht="22" customHeight="1"/>
+    <row r="15" ht="22" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="19" ht="22" customHeight="1"/>
+    <row r="20" ht="22" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1"/>
+    <row r="23" ht="22" customHeight="1"/>
+    <row r="24" ht="22" customHeight="1"/>
+    <row r="25" ht="22" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1"/>
+    <row r="27" ht="22" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1"/>
+    <row r="30" ht="22" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1"/>
+    <row r="36" ht="22" customHeight="1"/>
+    <row r="37" ht="22" customHeight="1"/>
+    <row r="38" ht="22" customHeight="1"/>
+    <row r="39" ht="22" customHeight="1"/>
+    <row r="40" ht="22" customHeight="1"/>
+    <row r="41" ht="22" customHeight="1"/>
+    <row r="42" ht="22" customHeight="1"/>
+    <row r="43" ht="22" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" tooltip="https://t-solo-api-game.ahameet.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D6" r:id="rId2" xr:uid="{05D80BFC-4931-48DB-8CC7-8F6D9770507D}"/>
-    <hyperlink ref="D7" r:id="rId3" xr:uid="{7C154214-A582-4C6E-B907-28F9AF6D0DFC}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" tooltip="https://t-solo-api-game.ahameet.com" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="13" defaultRowHeight="14.15"/>
+  <cols>
+    <col width="12" customWidth="1" style="1" min="1" max="1"/>
+    <col width="37" customWidth="1" style="3" min="2" max="24"/>
+    <col width="13" customWidth="1" style="2" min="25" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>网络域名表（NetHosts）</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="4" t="n"/>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="4" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="4" t="n"/>
+      <c r="W1" s="4" t="n"/>
+      <c r="X1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>#Desc</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+      <c r="P2" s="5" t="n"/>
+      <c r="Q2" s="5" t="n"/>
+      <c r="R2" s="5" t="n"/>
+      <c r="S2" s="5" t="n"/>
+      <c r="T2" s="5" t="n"/>
+      <c r="U2" s="5" t="n"/>
+      <c r="V2" s="5" t="n"/>
+      <c r="W2" s="5" t="n"/>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
+      <c r="N3" s="6" t="n"/>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="6" t="n"/>
+      <c r="Q3" s="6" t="n"/>
+      <c r="R3" s="6" t="n"/>
+      <c r="S3" s="6" t="n"/>
+      <c r="T3" s="6" t="n"/>
+      <c r="U3" s="6" t="n"/>
+      <c r="V3" s="6" t="n"/>
+      <c r="W3" s="6" t="n"/>
+      <c r="X3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="22" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>主机唯一标识名</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>GameServer</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>游戏服务器域名</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>https://t-solo-api-game.ahameet.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>TGAServer</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>游戏服务器域名</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>https://report.lolipopmobi.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>IAPServer</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>游戏支付服务器域名</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>https://t-pay-v3.ahameet.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1"/>
+    <row r="9" ht="22" customHeight="1"/>
+    <row r="10" ht="22" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1"/>
+    <row r="12" ht="22" customHeight="1"/>
+    <row r="13" ht="22" customHeight="1"/>
+    <row r="14" ht="22" customHeight="1"/>
+    <row r="15" ht="22" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="19" ht="22" customHeight="1"/>
+    <row r="20" ht="22" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1"/>
+    <row r="23" ht="22" customHeight="1"/>
+    <row r="24" ht="22" customHeight="1"/>
+    <row r="25" ht="22" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1"/>
+    <row r="27" ht="22" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1"/>
+    <row r="30" ht="22" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1"/>
+    <row r="36" ht="22" customHeight="1"/>
+    <row r="37" ht="22" customHeight="1"/>
+    <row r="38" ht="22" customHeight="1"/>
+    <row r="39" ht="22" customHeight="1"/>
+    <row r="40" ht="22" customHeight="1"/>
+    <row r="41" ht="22" customHeight="1"/>
+    <row r="42" ht="22" customHeight="1"/>
+    <row r="43" ht="22" customHeight="1"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" tooltip="https://t-solo-api-game.ahameet.com" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Assets/Samples/IAPDemo/Excels/Networks/HostKeys/NetworkHostKeys.xlsx
+++ b/Assets/Samples/IAPDemo/Excels/Networks/HostKeys/NetworkHostKeys.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="29">
   <si>
     <t>##comment</t>
   </si>
@@ -106,6 +106,15 @@
   <si>
     <t>https://t-payments.solotopiax.com</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FallbackValue</t>
+  </si>
+  <si>
+    <t>主域名</t>
+  </si>
+  <si>
+    <t>备用域名</t>
   </si>
 </sst>
 </file>
@@ -620,7 +629,9 @@
       <c r="D2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -654,7 +665,9 @@
       <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -686,7 +699,10 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -699,6 +715,9 @@
       <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="E5" s="7" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
@@ -710,6 +729,9 @@
       <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="E6" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
@@ -721,6 +743,9 @@
       <c r="D7" s="7" t="s">
         <v>22</v>
       </c>
+      <c r="E7" s="7" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
@@ -732,6 +757,9 @@
       <c r="D8" s="7" t="s">
         <v>22</v>
       </c>
+      <c r="E8" s="7" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="9" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
@@ -741,6 +769,9 @@
         <v>24</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -782,10 +813,15 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" tooltip="https://t-solo-api-game.ahameet.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E5" r:id="rId1" tooltip="https://t-solo-api-game.ahameet.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="D6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="D8" r:id="rId4" xr:uid="{4A9895B5-FA1E-4E9B-8ADC-D73489DFF848}"/>
+    <hyperlink ref="E8" r:id="rId4" xr:uid="{4A9895B5-FA1E-4E9B-8ADC-D73489DFF848}"/>
     <hyperlink ref="D9" r:id="rId5" xr:uid="{06AC7C6F-AF32-4044-A73C-25DBBC2FF81A}"/>
+    <hyperlink ref="E9" r:id="rId5" xr:uid="{06AC7C6F-AF32-4044-A73C-25DBBC2FF81A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
@@ -846,7 +882,9 @@
       <c r="D2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -880,7 +918,9 @@
       <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -912,7 +952,10 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -925,6 +968,9 @@
       <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="E5" s="7" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
@@ -936,6 +982,9 @@
       <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="E6" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
@@ -947,6 +996,9 @@
       <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
+      <c r="E7" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
@@ -958,6 +1010,9 @@
       <c r="D8" s="7" t="s">
         <v>22</v>
       </c>
+      <c r="E8" s="7" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="9" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
@@ -967,6 +1022,9 @@
         <v>24</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1008,10 +1066,15 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" tooltip="https://t-solo-api-game.ahameet.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="E5" r:id="rId1" tooltip="https://t-solo-api-game.ahameet.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="D6" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="E6" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="E7" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
     <hyperlink ref="D8" r:id="rId4" xr:uid="{1585AF03-04DA-47C6-A7C9-D24FB2F8CA60}"/>
+    <hyperlink ref="E8" r:id="rId4" xr:uid="{1585AF03-04DA-47C6-A7C9-D24FB2F8CA60}"/>
     <hyperlink ref="D9" r:id="rId5" xr:uid="{36AA8FA0-9428-43BB-99F6-0B30FB88A3CD}"/>
+    <hyperlink ref="E9" r:id="rId5" xr:uid="{36AA8FA0-9428-43BB-99F6-0B30FB88A3CD}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/Samples/IAPDemo/Excels/Networks/HostKeys/NetworkHostKeys.xlsx
+++ b/Assets/Samples/IAPDemo/Excels/Networks/HostKeys/NetworkHostKeys.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SoloGames-X\nova\Assets\Samples\IAPDemo\Excels\Networks\HostKeys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895E3F67-9116-4166-A9FB-91E0DD832554}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61166E6D-1C61-4CED-9E71-6A525CFCDF9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8130" yWindow="3060" windowWidth="24080" windowHeight="13160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>##comment</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>描述</t>
-  </si>
-  <si>
-    <t>URL</t>
   </si>
   <si>
     <t>GameServer</t>
@@ -133,6 +130,7 @@
       <sz val="9.75"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -140,6 +138,7 @@
       <sz val="9.75"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -148,6 +147,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -630,7 +630,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -699,80 +699,80 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>22</v>
-      </c>
       <c r="E8" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -813,24 +813,24 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" tooltip="https://t-solo-api-game.ahameet.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E5" r:id="rId1" tooltip="https://t-solo-api-game.ahameet.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="E6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="E7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D8" r:id="rId4" xr:uid="{4A9895B5-FA1E-4E9B-8ADC-D73489DFF848}"/>
-    <hyperlink ref="E8" r:id="rId4" xr:uid="{4A9895B5-FA1E-4E9B-8ADC-D73489DFF848}"/>
-    <hyperlink ref="D9" r:id="rId5" xr:uid="{06AC7C6F-AF32-4044-A73C-25DBBC2FF81A}"/>
-    <hyperlink ref="E9" r:id="rId5" xr:uid="{06AC7C6F-AF32-4044-A73C-25DBBC2FF81A}"/>
+    <hyperlink ref="E5" r:id="rId2" tooltip="https://t-solo-api-game.ahameet.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{4A9895B5-FA1E-4E9B-8ADC-D73489DFF848}"/>
+    <hyperlink ref="E8" r:id="rId8" xr:uid="{4A9895B5-FA1E-4E9B-8ADC-D73489DFF848}"/>
+    <hyperlink ref="D9" r:id="rId9" xr:uid="{06AC7C6F-AF32-4044-A73C-25DBBC2FF81A}"/>
+    <hyperlink ref="E9" r:id="rId10" xr:uid="{06AC7C6F-AF32-4044-A73C-25DBBC2FF81A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:X43"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
@@ -883,7 +883,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -952,82 +952,69 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
+    </row>
+    <row r="9" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1061,20 +1048,17 @@
     <row r="40" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" tooltip="https://t-solo-api-game.ahameet.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="E5" r:id="rId1" tooltip="https://t-solo-api-game.ahameet.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="D6" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="E6" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="E7" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="D8" r:id="rId4" xr:uid="{1585AF03-04DA-47C6-A7C9-D24FB2F8CA60}"/>
-    <hyperlink ref="E8" r:id="rId4" xr:uid="{1585AF03-04DA-47C6-A7C9-D24FB2F8CA60}"/>
-    <hyperlink ref="D9" r:id="rId5" xr:uid="{36AA8FA0-9428-43BB-99F6-0B30FB88A3CD}"/>
-    <hyperlink ref="E9" r:id="rId5" xr:uid="{36AA8FA0-9428-43BB-99F6-0B30FB88A3CD}"/>
+    <hyperlink ref="E5" r:id="rId2" tooltip="https://t-solo-api-game.ahameet.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="D6" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="E6" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="D8" r:id="rId6" xr:uid="{36AA8FA0-9428-43BB-99F6-0B30FB88A3CD}"/>
+    <hyperlink ref="E8" r:id="rId7" xr:uid="{36AA8FA0-9428-43BB-99F6-0B30FB88A3CD}"/>
+    <hyperlink ref="E7" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
